--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.12069714527595</v>
+        <v>12.04461328610734</v>
       </c>
       <c r="D2" t="n">
-        <v>37</v>
+        <v>6.0125</v>
       </c>
       <c r="E2" t="n">
-        <v>22.73760939438908</v>
+        <v>3.694861526588225</v>
       </c>
       <c r="F2" t="n">
-        <v>14.1224107297721</v>
+        <v>2.294891743587966</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.18002072158905</v>
+        <v>9.616753367258221</v>
       </c>
       <c r="D3" t="n">
-        <v>31.84422686422923</v>
+        <v>5.17468686543725</v>
       </c>
       <c r="E3" t="n">
-        <v>22.73760939438908</v>
+        <v>3.694861526588225</v>
       </c>
       <c r="F3" t="n">
-        <v>14.1224107297721</v>
+        <v>2.294891743587966</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.18448860503812</v>
+        <v>3.279979398318694</v>
       </c>
       <c r="D4" t="n">
-        <v>64.04566291932272</v>
+        <v>10.40742022438994</v>
       </c>
       <c r="E4" t="n">
-        <v>22.73760939438908</v>
+        <v>3.694861526588225</v>
       </c>
       <c r="F4" t="n">
-        <v>14.1224107297721</v>
+        <v>2.294891743587966</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
